--- a/static/data/exports/Retro_KL_GE_2009.xlsx
+++ b/static/data/exports/Retro_KL_GE_2009.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/static/data/exports/Retro_KL_GE_2009.xlsx
+++ b/static/data/exports/Retro_KL_GE_2009.xlsx
@@ -88819,11 +88819,11 @@
     </row>
     <row r="1426">
       <c r="A1426" t="n">
-        <v>1709701</v>
+        <v>1709700</v>
       </c>
       <c r="B1426" t="inlineStr">
         <is>
-          <t>Dileep</t>
+          <t>U.Nahur Miran Peeru Muhammad</t>
         </is>
       </c>
       <c r="C1426" t="inlineStr">
@@ -88856,7 +88856,7 @@
       </c>
       <c r="K1426" t="inlineStr">
         <is>
-          <t>Dileep</t>
+          <t>U.Nahur Miran Peeru Muhammad</t>
         </is>
       </c>
       <c r="L1426" t="inlineStr">
@@ -88881,11 +88881,11 @@
     </row>
     <row r="1427">
       <c r="A1427" t="n">
-        <v>1709700</v>
+        <v>1709701</v>
       </c>
       <c r="B1427" t="inlineStr">
         <is>
-          <t>U.Nahur Miran Peeru Muhammad</t>
+          <t>Dileep</t>
         </is>
       </c>
       <c r="C1427" t="inlineStr">
@@ -88918,7 +88918,7 @@
       </c>
       <c r="K1427" t="inlineStr">
         <is>
-          <t>U.Nahur Miran Peeru Muhammad</t>
+          <t>Dileep</t>
         </is>
       </c>
       <c r="L1427" t="inlineStr">
